--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T11:16:18+00:00</t>
+    <t>2025-08-22T11:39:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2019,7 +2019,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T11:39:32+00:00</t>
+    <t>2025-08-22T13:00:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T13:00:58+00:00</t>
+    <t>2025-08-22T15:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2019,7 +2019,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T15:38:31+00:00</t>
+    <t>2025-08-22T16:16:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2019,7 +2019,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T16:16:41+00:00</t>
+    <t>2025-08-25T07:57:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/qa-correction-erreurs/ig/StructureDefinition-fr-core-assigned-author.xlsx
+++ b/qa-correction-erreurs/ig/StructureDefinition-fr-core-assigned-author.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T07:57:03+00:00</t>
+    <t>2025-08-25T14:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
